--- a/outputs/barcelona_samples_2019_2023.xlsx
+++ b/outputs/barcelona_samples_2019_2023.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="78" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -64,7 +64,7 @@
     <t xml:space="preserve">tract_0009</t>
   </si>
   <si>
-    <t xml:space="preserve">all</t>
+    <t xml:space="preserve">D1_C2</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.41549,2.173345</t>
@@ -85,6 +85,9 @@
     <t xml:space="preserve">tract_0011</t>
   </si>
   <si>
+    <t xml:space="preserve">D1_C3</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3874746,2.1587447</t>
   </si>
   <si>
@@ -100,24 +103,36 @@
     <t xml:space="preserve">tract_0025</t>
   </si>
   <si>
+    <t xml:space="preserve">D2_C2</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414948,2.186892</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0027</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937459,2.1788945</t>
+    <t xml:space="preserve">D2_C3</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3932077,2.1781582</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0031</t>
   </si>
   <si>
+    <t xml:space="preserve">D3_C1</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3756794,2.123406</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0039</t>
   </si>
   <si>
+    <t xml:space="preserve">D3_C2</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3728226,2.1464894</t>
   </si>
   <si>
@@ -127,6 +142,9 @@
     <t xml:space="preserve">tract_0041</t>
   </si>
   <si>
+    <t xml:space="preserve">D3_C3</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4044252,2.1788391</t>
   </si>
   <si>
@@ -157,6 +175,9 @@
     <t xml:space="preserve">tract_0003</t>
   </si>
   <si>
+    <t xml:space="preserve">D1_C1</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4514103,2.1767584</t>
   </si>
   <si>
@@ -172,6 +193,9 @@
     <t xml:space="preserve">tract_0019</t>
   </si>
   <si>
+    <t xml:space="preserve">D2_C1</t>
+  </si>
+  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4325914,2.179213</t>
   </si>
   <si>
@@ -181,13 +205,13 @@
     <t xml:space="preserve">GENERAL</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4152147,2.1735227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4144238,2.1724705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4194662,2.2080986</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127982,2.176309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4155369,2.1747833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4216081,2.2065221</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.418463,2.2068953</t>
@@ -196,13 +220,13 @@
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3883722,2.1571174</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3878616,2.1600354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3886571,2.1985625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3868026,2.1981063</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3854603,2.1629924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3910704,2.2027593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3913701,2.198509</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414303,2.1842145</t>
@@ -220,7 +244,7 @@
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780213,2.1239693</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3764011,2.1259979</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780993,2.1268182</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3712013,2.1440509</t>
@@ -232,16 +256,13 @@
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4059407666011,2.18071500409385</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3822595,2.1495737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827419,2.1485438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3806554,2.1517466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3806556,2.1516589</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815253,2.1503529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827831,2.1489247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3812655,2.1526398</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936</t>
@@ -756,7 +777,7 @@
         <v>22</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>2.1587447</v>
@@ -765,7 +786,7 @@
         <v>41.3874746</v>
       </c>
       <c r="G5" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3874746,2.1587447","Open GSV")</f>
@@ -790,7 +811,7 @@
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>2.1650949</v>
@@ -799,7 +820,7 @@
         <v>41.387157</v>
       </c>
       <c r="G6" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="H6" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.387157,2.1650949","Open GSV")</f>
@@ -821,10 +842,10 @@
         <v>14</v>
       </c>
       <c r="C7" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
         <v>2.1986922</v>
@@ -833,7 +854,7 @@
         <v>41.3903675</v>
       </c>
       <c r="G7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="H7" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3903675,2.1986922","Open GSV")</f>
@@ -855,10 +876,10 @@
         <v>14</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E8" t="n">
         <v>2.186892</v>
@@ -867,7 +888,7 @@
         <v>41.414948</v>
       </c>
       <c r="G8" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="H8" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414948,2.186892","Open GSV")</f>
@@ -889,22 +910,22 @@
         <v>14</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1788945</v>
+        <v>2.1781582</v>
       </c>
       <c r="F9" t="n">
-        <v>41.3937459</v>
+        <v>41.3932077</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>33</v>
       </c>
       <c r="H9" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937459,2.1788945","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3932077,2.1781582","Open GSV")</f>
       </c>
       <c r="I9" t="s">
         <v>18</v>
@@ -923,10 +944,10 @@
         <v>14</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>2.123406</v>
@@ -935,7 +956,7 @@
         <v>41.3756794</v>
       </c>
       <c r="G10" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3756794,2.123406","Open GSV")</f>
@@ -957,10 +978,10 @@
         <v>14</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E11" t="n">
         <v>2.1464894</v>
@@ -969,7 +990,7 @@
         <v>41.3728226</v>
       </c>
       <c r="G11" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="H11" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3728226,2.1464894","Open GSV")</f>
@@ -991,10 +1012,10 @@
         <v>14</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E12" t="n">
         <v>2.1431141</v>
@@ -1003,7 +1024,7 @@
         <v>41.3702902</v>
       </c>
       <c r="G12" t="s">
-        <v>35</v>
+        <v>40</v>
       </c>
       <c r="H12" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3702902,2.1431141","Open GSV")</f>
@@ -1025,10 +1046,10 @@
         <v>14</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>2.1788391</v>
@@ -1037,7 +1058,7 @@
         <v>41.4044252</v>
       </c>
       <c r="G13" t="s">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="H13" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4044252,2.1788391","Open GSV")</f>
@@ -1059,10 +1080,10 @@
         <v>14</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E14" t="n">
         <v>2.1809344</v>
@@ -1071,7 +1092,7 @@
         <v>41.4045602</v>
       </c>
       <c r="G14" t="s">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="H14" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4045602,2.1809344","Open GSV")</f>
@@ -1093,10 +1114,10 @@
         <v>14</v>
       </c>
       <c r="C15" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
         <v>2.1491612</v>
@@ -1105,7 +1126,7 @@
         <v>41.3820983</v>
       </c>
       <c r="G15" t="s">
-        <v>40</v>
+        <v>46</v>
       </c>
       <c r="H15" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3820983,2.1491612","Open GSV")</f>
@@ -1127,10 +1148,10 @@
         <v>14</v>
       </c>
       <c r="C16" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
         <v>2.1503594</v>
@@ -1139,7 +1160,7 @@
         <v>41.3811841</v>
       </c>
       <c r="G16" t="s">
-        <v>42</v>
+        <v>48</v>
       </c>
       <c r="H16" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3811841,2.1503594","Open GSV")</f>
@@ -1161,10 +1182,10 @@
         <v>14</v>
       </c>
       <c r="C17" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
         <v>2.1475377</v>
@@ -1173,7 +1194,7 @@
         <v>41.3825524</v>
       </c>
       <c r="G17" t="s">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="H17" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3825524,2.1475377","Open GSV")</f>
@@ -1264,13 +1285,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C2" t="s">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>53</v>
       </c>
       <c r="E2" t="n">
         <v>2.1767584</v>
@@ -1279,7 +1300,7 @@
         <v>41.4514103</v>
       </c>
       <c r="G2" t="s">
-        <v>47</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4514103,2.1767584","Open GSV")</f>
@@ -1298,7 +1319,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C3" t="s">
         <v>20</v>
@@ -1313,7 +1334,7 @@
         <v>41.4201897</v>
       </c>
       <c r="G3" t="s">
-        <v>48</v>
+        <v>55</v>
       </c>
       <c r="H3" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4201897,2.2076764","Open GSV")</f>
@@ -1332,13 +1353,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C4" t="s">
         <v>22</v>
       </c>
       <c r="D4" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E4" t="n">
         <v>2.161863</v>
@@ -1347,7 +1368,7 @@
         <v>41.3881553</v>
       </c>
       <c r="G4" t="s">
-        <v>49</v>
+        <v>56</v>
       </c>
       <c r="H4" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3881553,2.161863","Open GSV")</f>
@@ -1366,13 +1387,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E5" t="n">
         <v>2.2052854</v>
@@ -1381,7 +1402,7 @@
         <v>41.3931534</v>
       </c>
       <c r="G5" t="s">
-        <v>50</v>
+        <v>57</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3931534,2.2052854","Open GSV")</f>
@@ -1400,13 +1421,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>58</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>59</v>
       </c>
       <c r="E6" t="n">
         <v>2.179213</v>
@@ -1415,7 +1436,7 @@
         <v>41.4325914</v>
       </c>
       <c r="G6" t="s">
-        <v>52</v>
+        <v>60</v>
       </c>
       <c r="H6" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4325914,2.179213","Open GSV")</f>
@@ -1434,13 +1455,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>45</v>
+        <v>51</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E7" t="n">
         <v>2.1866863</v>
@@ -1449,7 +1470,7 @@
         <v>41.4147464</v>
       </c>
       <c r="G7" t="s">
-        <v>53</v>
+        <v>61</v>
       </c>
       <c r="H7" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4147464,2.1866863","Open GSV")</f>
@@ -1540,7 +1561,7 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C2" t="s">
         <v>15</v>
@@ -1549,16 +1570,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>2.1735227</v>
+        <v>2.176309</v>
       </c>
       <c r="F2" t="n">
-        <v>41.4152147</v>
+        <v>41.4127982</v>
       </c>
       <c r="G2" t="s">
-        <v>55</v>
+        <v>63</v>
       </c>
       <c r="H2" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4152147,2.1735227","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127982,2.176309","Open GSV")</f>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -1574,7 +1595,7 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C3" t="s">
         <v>15</v>
@@ -1583,16 +1604,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1724705</v>
+        <v>2.1747833</v>
       </c>
       <c r="F3" t="n">
-        <v>41.4144238</v>
+        <v>41.4155369</v>
       </c>
       <c r="G3" t="s">
-        <v>56</v>
+        <v>64</v>
       </c>
       <c r="H3" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4144238,2.1724705","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4155369,2.1747833","Open GSV")</f>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -1608,7 +1629,7 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C4" t="s">
         <v>20</v>
@@ -1617,16 +1638,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2080986</v>
+        <v>2.2065221</v>
       </c>
       <c r="F4" t="n">
-        <v>41.4194662</v>
+        <v>41.4216081</v>
       </c>
       <c r="G4" t="s">
-        <v>57</v>
+        <v>65</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4194662,2.2080986","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4216081,2.2065221","Open GSV")</f>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1642,7 +1663,7 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C5" t="s">
         <v>20</v>
@@ -1657,7 +1678,7 @@
         <v>41.418463</v>
       </c>
       <c r="G5" t="s">
-        <v>58</v>
+        <v>66</v>
       </c>
       <c r="H5" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.418463,2.2068953","Open GSV")</f>
@@ -1676,13 +1697,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C6" t="s">
         <v>22</v>
       </c>
       <c r="D6" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E6" t="n">
         <v>2.1571174</v>
@@ -1691,7 +1712,7 @@
         <v>41.3883722</v>
       </c>
       <c r="G6" t="s">
-        <v>59</v>
+        <v>67</v>
       </c>
       <c r="H6" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3883722,2.1571174","Open GSV")</f>
@@ -1710,25 +1731,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C7" t="s">
         <v>22</v>
       </c>
       <c r="D7" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1600354</v>
+        <v>2.1629924</v>
       </c>
       <c r="F7" t="n">
-        <v>41.3878616</v>
+        <v>41.3854603</v>
       </c>
       <c r="G7" t="s">
-        <v>60</v>
+        <v>68</v>
       </c>
       <c r="H7" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3878616,2.1600354","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3854603,2.1629924","Open GSV")</f>
       </c>
       <c r="I7" t="s">
         <v>18</v>
@@ -1744,25 +1765,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D8" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>2.1985625</v>
+        <v>2.2027593</v>
       </c>
       <c r="F8" t="n">
-        <v>41.3886571</v>
+        <v>41.3910704</v>
       </c>
       <c r="G8" t="s">
-        <v>61</v>
+        <v>69</v>
       </c>
       <c r="H8" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3886571,2.1985625","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3910704,2.2027593","Open GSV")</f>
       </c>
       <c r="I8" t="s">
         <v>18</v>
@@ -1778,25 +1799,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D9" t="s">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>2.1981063</v>
+        <v>2.198509</v>
       </c>
       <c r="F9" t="n">
-        <v>41.3868026</v>
+        <v>41.3913701</v>
       </c>
       <c r="G9" t="s">
-        <v>62</v>
+        <v>70</v>
       </c>
       <c r="H9" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3868026,2.1981063","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3913701,2.198509","Open GSV")</f>
       </c>
       <c r="I9" t="s">
         <v>18</v>
@@ -1812,13 +1833,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E10" t="n">
         <v>2.1842145</v>
@@ -1827,7 +1848,7 @@
         <v>41.414303</v>
       </c>
       <c r="G10" t="s">
-        <v>63</v>
+        <v>71</v>
       </c>
       <c r="H10" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414303,2.1842145","Open GSV")</f>
@@ -1846,13 +1867,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11" t="s">
-        <v>16</v>
+        <v>29</v>
       </c>
       <c r="E11" t="n">
         <v>2.184027</v>
@@ -1861,7 +1882,7 @@
         <v>41.4147952</v>
       </c>
       <c r="G11" t="s">
-        <v>64</v>
+        <v>72</v>
       </c>
       <c r="H11" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4147952,2.184027","Open GSV")</f>
@@ -1880,13 +1901,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D12" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
         <v>2.1793069</v>
@@ -1895,7 +1916,7 @@
         <v>41.3937497</v>
       </c>
       <c r="G12" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="H12" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937497,2.1793069","Open GSV")</f>
@@ -1914,13 +1935,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D13" t="s">
-        <v>16</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
         <v>2.1779367</v>
@@ -1929,7 +1950,7 @@
         <v>41.3947872</v>
       </c>
       <c r="G13" t="s">
-        <v>66</v>
+        <v>74</v>
       </c>
       <c r="H13" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3947872,2.1779367","Open GSV")</f>
@@ -1948,13 +1969,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E14" t="n">
         <v>2.1239693</v>
@@ -1963,7 +1984,7 @@
         <v>41.3780213</v>
       </c>
       <c r="G14" t="s">
-        <v>67</v>
+        <v>75</v>
       </c>
       <c r="H14" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780213,2.1239693","Open GSV")</f>
@@ -1982,25 +2003,25 @@
         <v>14</v>
       </c>
       <c r="B15" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>16</v>
+        <v>35</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1259979</v>
+        <v>2.1268182</v>
       </c>
       <c r="F15" t="n">
-        <v>41.3764011</v>
+        <v>41.3780993</v>
       </c>
       <c r="G15" t="s">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="H15" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3764011,2.1259979","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780993,2.1268182","Open GSV")</f>
       </c>
       <c r="I15" t="s">
         <v>18</v>
@@ -2016,13 +2037,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D16" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E16" t="n">
         <v>2.1440509</v>
@@ -2031,7 +2052,7 @@
         <v>41.3712013</v>
       </c>
       <c r="G16" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="H16" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3712013,2.1440509","Open GSV")</f>
@@ -2050,13 +2071,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
       <c r="D17" t="s">
-        <v>16</v>
+        <v>38</v>
       </c>
       <c r="E17" t="n">
         <v>2.147403</v>
@@ -2065,7 +2086,7 @@
         <v>41.3719318</v>
       </c>
       <c r="G17" t="s">
-        <v>70</v>
+        <v>78</v>
       </c>
       <c r="H17" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3719318,2.147403","Open GSV")</f>
@@ -2084,13 +2105,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C18" t="s">
-        <v>36</v>
+        <v>41</v>
       </c>
       <c r="D18" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E18" t="n">
         <v>2.18071500409385</v>
@@ -2099,7 +2120,7 @@
         <v>41.4059407666011</v>
       </c>
       <c r="G18" t="s">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="H18" s="1" t="str">
         <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4059407666011,2.18071500409385","Open GSV")</f>
@@ -2118,25 +2139,25 @@
         <v>18</v>
       </c>
       <c r="B19" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C19" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D19" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E19" t="n">
-        <v>2.1495737</v>
+        <v>2.1503529</v>
       </c>
       <c r="F19" t="n">
-        <v>41.3822595</v>
+        <v>41.3815253</v>
       </c>
       <c r="G19" t="s">
-        <v>72</v>
+        <v>80</v>
       </c>
       <c r="H19" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3822595,2.1495737","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815253,2.1503529","Open GSV")</f>
       </c>
       <c r="I19" t="s">
         <v>18</v>
@@ -2152,25 +2173,25 @@
         <v>19</v>
       </c>
       <c r="B20" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C20" t="s">
-        <v>39</v>
+        <v>45</v>
       </c>
       <c r="D20" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E20" t="n">
-        <v>2.1485438</v>
+        <v>2.1489247</v>
       </c>
       <c r="F20" t="n">
-        <v>41.3827419</v>
+        <v>41.3827831</v>
       </c>
       <c r="G20" t="s">
-        <v>73</v>
+        <v>81</v>
       </c>
       <c r="H20" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827419,2.1485438","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827831,2.1489247","Open GSV")</f>
       </c>
       <c r="I20" t="s">
         <v>18</v>
@@ -2186,25 +2207,25 @@
         <v>20</v>
       </c>
       <c r="B21" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C21" t="s">
-        <v>41</v>
+        <v>47</v>
       </c>
       <c r="D21" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E21" t="n">
-        <v>2.1517466</v>
+        <v>2.1526398</v>
       </c>
       <c r="F21" t="n">
-        <v>41.3806554</v>
+        <v>41.3812655</v>
       </c>
       <c r="G21" t="s">
-        <v>74</v>
+        <v>82</v>
       </c>
       <c r="H21" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3806554,2.1517466","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3812655,2.1526398","Open GSV")</f>
       </c>
       <c r="I21" t="s">
         <v>18</v>
@@ -2220,25 +2241,25 @@
         <v>21</v>
       </c>
       <c r="B22" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C22" t="s">
-        <v>41</v>
+        <v>49</v>
       </c>
       <c r="D22" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E22" t="n">
-        <v>2.1516589</v>
+        <v>2.1485936</v>
       </c>
       <c r="F22" t="n">
-        <v>41.3806556</v>
+        <v>41.3828476</v>
       </c>
       <c r="G22" t="s">
-        <v>75</v>
+        <v>83</v>
       </c>
       <c r="H22" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3806556,2.1516589","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936","Open GSV")</f>
       </c>
       <c r="I22" t="s">
         <v>18</v>
@@ -2254,25 +2275,25 @@
         <v>22</v>
       </c>
       <c r="B23" t="s">
-        <v>54</v>
+        <v>62</v>
       </c>
       <c r="C23" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="D23" t="s">
-        <v>16</v>
+        <v>42</v>
       </c>
       <c r="E23" t="n">
-        <v>2.1485936</v>
+        <v>2.1481751</v>
       </c>
       <c r="F23" t="n">
-        <v>41.3828476</v>
+        <v>41.3828211</v>
       </c>
       <c r="G23" t="s">
-        <v>76</v>
+        <v>84</v>
       </c>
       <c r="H23" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828211,2.1481751","Open GSV")</f>
       </c>
       <c r="I23" t="s">
         <v>18</v>
@@ -2282,40 +2303,6 @@
       <c r="L23"/>
       <c r="M23"/>
       <c r="N23"/>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>23</v>
-      </c>
-      <c r="B24" t="s">
-        <v>54</v>
-      </c>
-      <c r="C24" t="s">
-        <v>43</v>
-      </c>
-      <c r="D24" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.1481751</v>
-      </c>
-      <c r="F24" t="n">
-        <v>41.3828211</v>
-      </c>
-      <c r="G24" t="s">
-        <v>77</v>
-      </c>
-      <c r="H24" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828211,2.1481751","Open GSV")</f>
-      </c>
-      <c r="I24" t="s">
-        <v>18</v>
-      </c>
-      <c r="J24"/>
-      <c r="K24"/>
-      <c r="L24"/>
-      <c r="M24"/>
-      <c r="N24"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>

--- a/outputs/barcelona_samples_2019_2023.xlsx
+++ b/outputs/barcelona_samples_2019_2023.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="79">
   <si>
     <t xml:space="preserve">id</t>
   </si>
@@ -145,10 +145,10 @@
     <t xml:space="preserve">D3_C3</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4044252,2.1788391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4045602,2.1809344</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4042666,2.178625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4050698,2.1802922</t>
   </si>
   <si>
     <t xml:space="preserve">tract_0042</t>
@@ -184,7 +184,7 @@
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4201897,2.2076764</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3881553,2.161863</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3860404,2.1590386</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3931534,2.2052854</t>
@@ -205,70 +205,52 @@
     <t xml:space="preserve">GENERAL</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127982,2.176309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4155369,2.1747833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4216081,2.2065221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.418463,2.2068953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3883722,2.1571174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3854603,2.1629924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3910704,2.2027593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3913701,2.198509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414303,2.1842145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4147952,2.184027</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4133995,2.1711025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4144238,2.1724705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4194662,2.2080986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4213576,2.2084724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3866425,2.1597809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3864939,2.1595943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3916384,2.2008184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.387955,2.1995116</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937497,2.1793069</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3947872,2.1779367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780213,2.1239693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780993,2.1268182</t>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.377109,2.1275899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3777898,2.1247183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3719318,2.147403</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3712013,2.1440509</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3719318,2.147403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4059407666011,2.18071500409385</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815253,2.1503529</t>
   </si>
   <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827831,2.1489247</t>
-  </si>
-  <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3812655,2.1526398</t>
   </si>
   <si>
     <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828211,2.1481751</t>
   </si>
 </sst>
 </file>
@@ -1052,16 +1034,16 @@
         <v>42</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1788391</v>
+        <v>2.178625</v>
       </c>
       <c r="F13" t="n">
-        <v>41.4044252</v>
+        <v>41.4042666</v>
       </c>
       <c r="G13" t="s">
         <v>43</v>
       </c>
       <c r="H13" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4044252,2.1788391","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4042666,2.178625","Open GSV")</f>
       </c>
       <c r="I13" t="s">
         <v>18</v>
@@ -1086,16 +1068,16 @@
         <v>42</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1809344</v>
+        <v>2.1802922</v>
       </c>
       <c r="F14" t="n">
-        <v>41.4045602</v>
+        <v>41.4050698</v>
       </c>
       <c r="G14" t="s">
         <v>44</v>
       </c>
       <c r="H14" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4045602,2.1809344","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4050698,2.1802922","Open GSV")</f>
       </c>
       <c r="I14" t="s">
         <v>18</v>
@@ -1362,16 +1344,16 @@
         <v>23</v>
       </c>
       <c r="E4" t="n">
-        <v>2.161863</v>
+        <v>2.1590386</v>
       </c>
       <c r="F4" t="n">
-        <v>41.3881553</v>
+        <v>41.3860404</v>
       </c>
       <c r="G4" t="s">
         <v>56</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3881553,2.161863","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3860404,2.1590386","Open GSV")</f>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1500,9 +1482,9 @@
     <col min="2" max="2" width="7.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="10.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="7.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="11.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="11.71" hidden="0" customWidth="1"/>
-    <col min="7" max="7" width="103.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="9.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="10.71" hidden="0" customWidth="1"/>
+    <col min="7" max="7" width="90.71" hidden="0" customWidth="1"/>
     <col min="8" max="8" width="3.71" hidden="0" customWidth="1"/>
     <col min="9" max="9" width="11.71" hidden="0" customWidth="1"/>
     <col min="10" max="10" width="12.71" hidden="0" customWidth="1"/>
@@ -1570,16 +1552,16 @@
         <v>16</v>
       </c>
       <c r="E2" t="n">
-        <v>2.176309</v>
+        <v>2.1711025</v>
       </c>
       <c r="F2" t="n">
-        <v>41.4127982</v>
+        <v>41.4133995</v>
       </c>
       <c r="G2" t="s">
         <v>63</v>
       </c>
       <c r="H2" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4127982,2.176309","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4133995,2.1711025","Open GSV")</f>
       </c>
       <c r="I2" t="s">
         <v>18</v>
@@ -1604,16 +1586,16 @@
         <v>16</v>
       </c>
       <c r="E3" t="n">
-        <v>2.1747833</v>
+        <v>2.1724705</v>
       </c>
       <c r="F3" t="n">
-        <v>41.4155369</v>
+        <v>41.4144238</v>
       </c>
       <c r="G3" t="s">
         <v>64</v>
       </c>
       <c r="H3" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4155369,2.1747833","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4144238,2.1724705","Open GSV")</f>
       </c>
       <c r="I3" t="s">
         <v>18</v>
@@ -1638,16 +1620,16 @@
         <v>16</v>
       </c>
       <c r="E4" t="n">
-        <v>2.2065221</v>
+        <v>2.2080986</v>
       </c>
       <c r="F4" t="n">
-        <v>41.4216081</v>
+        <v>41.4194662</v>
       </c>
       <c r="G4" t="s">
         <v>65</v>
       </c>
       <c r="H4" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4216081,2.2065221","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4194662,2.2080986","Open GSV")</f>
       </c>
       <c r="I4" t="s">
         <v>18</v>
@@ -1672,16 +1654,16 @@
         <v>16</v>
       </c>
       <c r="E5" t="n">
-        <v>2.2068953</v>
+        <v>2.2084724</v>
       </c>
       <c r="F5" t="n">
-        <v>41.418463</v>
+        <v>41.4213576</v>
       </c>
       <c r="G5" t="s">
         <v>66</v>
       </c>
       <c r="H5" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.418463,2.2068953","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4213576,2.2084724","Open GSV")</f>
       </c>
       <c r="I5" t="s">
         <v>18</v>
@@ -1706,16 +1688,16 @@
         <v>23</v>
       </c>
       <c r="E6" t="n">
-        <v>2.1571174</v>
+        <v>2.1597809</v>
       </c>
       <c r="F6" t="n">
-        <v>41.3883722</v>
+        <v>41.3866425</v>
       </c>
       <c r="G6" t="s">
         <v>67</v>
       </c>
       <c r="H6" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3883722,2.1571174","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3866425,2.1597809","Open GSV")</f>
       </c>
       <c r="I6" t="s">
         <v>18</v>
@@ -1740,16 +1722,16 @@
         <v>23</v>
       </c>
       <c r="E7" t="n">
-        <v>2.1629924</v>
+        <v>2.1595943</v>
       </c>
       <c r="F7" t="n">
-        <v>41.3854603</v>
+        <v>41.3864939</v>
       </c>
       <c r="G7" t="s">
         <v>68</v>
       </c>
       <c r="H7" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3854603,2.1629924","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3864939,2.1595943","Open GSV")</f>
       </c>
       <c r="I7" t="s">
         <v>18</v>
@@ -1774,16 +1756,16 @@
         <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>2.2027593</v>
+        <v>2.2008184</v>
       </c>
       <c r="F8" t="n">
-        <v>41.3910704</v>
+        <v>41.3916384</v>
       </c>
       <c r="G8" t="s">
         <v>69</v>
       </c>
       <c r="H8" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3910704,2.2027593","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3916384,2.2008184","Open GSV")</f>
       </c>
       <c r="I8" t="s">
         <v>18</v>
@@ -1808,16 +1790,16 @@
         <v>23</v>
       </c>
       <c r="E9" t="n">
-        <v>2.198509</v>
+        <v>2.1995116</v>
       </c>
       <c r="F9" t="n">
-        <v>41.3913701</v>
+        <v>41.387955</v>
       </c>
       <c r="G9" t="s">
         <v>70</v>
       </c>
       <c r="H9" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3913701,2.198509","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.387955,2.1995116","Open GSV")</f>
       </c>
       <c r="I9" t="s">
         <v>18</v>
@@ -1836,22 +1818,22 @@
         <v>62</v>
       </c>
       <c r="C10" t="s">
-        <v>28</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>2.1842145</v>
+        <v>2.1793069</v>
       </c>
       <c r="F10" t="n">
-        <v>41.414303</v>
+        <v>41.3937497</v>
       </c>
       <c r="G10" t="s">
         <v>71</v>
       </c>
       <c r="H10" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.414303,2.1842145","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937497,2.1793069","Open GSV")</f>
       </c>
       <c r="I10" t="s">
         <v>18</v>
@@ -1870,22 +1852,22 @@
         <v>62</v>
       </c>
       <c r="C11" t="s">
-        <v>28</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>29</v>
+        <v>35</v>
       </c>
       <c r="E11" t="n">
-        <v>2.184027</v>
+        <v>2.1275899</v>
       </c>
       <c r="F11" t="n">
-        <v>41.4147952</v>
+        <v>41.377109</v>
       </c>
       <c r="G11" t="s">
         <v>72</v>
       </c>
       <c r="H11" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4147952,2.184027","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.377109,2.1275899","Open GSV")</f>
       </c>
       <c r="I11" t="s">
         <v>18</v>
@@ -1904,22 +1886,22 @@
         <v>62</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E12" t="n">
-        <v>2.1793069</v>
+        <v>2.1247183</v>
       </c>
       <c r="F12" t="n">
-        <v>41.3937497</v>
+        <v>41.3777898</v>
       </c>
       <c r="G12" t="s">
         <v>73</v>
       </c>
       <c r="H12" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3937497,2.1793069","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3777898,2.1247183","Open GSV")</f>
       </c>
       <c r="I12" t="s">
         <v>18</v>
@@ -1938,22 +1920,22 @@
         <v>62</v>
       </c>
       <c r="C13" t="s">
-        <v>31</v>
+        <v>37</v>
       </c>
       <c r="D13" t="s">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1779367</v>
+        <v>2.147403</v>
       </c>
       <c r="F13" t="n">
-        <v>41.3947872</v>
+        <v>41.3719318</v>
       </c>
       <c r="G13" t="s">
         <v>74</v>
       </c>
       <c r="H13" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3947872,2.1779367","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3719318,2.147403","Open GSV")</f>
       </c>
       <c r="I13" t="s">
         <v>18</v>
@@ -1972,22 +1954,22 @@
         <v>62</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="D14" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
       <c r="E14" t="n">
-        <v>2.1239693</v>
+        <v>2.1440509</v>
       </c>
       <c r="F14" t="n">
-        <v>41.3780213</v>
+        <v>41.3712013</v>
       </c>
       <c r="G14" t="s">
         <v>75</v>
       </c>
       <c r="H14" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780213,2.1239693","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3712013,2.1440509","Open GSV")</f>
       </c>
       <c r="I14" t="s">
         <v>18</v>
@@ -2006,22 +1988,22 @@
         <v>62</v>
       </c>
       <c r="C15" t="s">
-        <v>34</v>
+        <v>45</v>
       </c>
       <c r="D15" t="s">
-        <v>35</v>
+        <v>42</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1268182</v>
+        <v>2.1503529</v>
       </c>
       <c r="F15" t="n">
-        <v>41.3780993</v>
+        <v>41.3815253</v>
       </c>
       <c r="G15" t="s">
         <v>76</v>
       </c>
       <c r="H15" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3780993,2.1268182","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815253,2.1503529","Open GSV")</f>
       </c>
       <c r="I15" t="s">
         <v>18</v>
@@ -2040,22 +2022,22 @@
         <v>62</v>
       </c>
       <c r="C16" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="D16" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1440509</v>
+        <v>2.1526398</v>
       </c>
       <c r="F16" t="n">
-        <v>41.3712013</v>
+        <v>41.3812655</v>
       </c>
       <c r="G16" t="s">
         <v>77</v>
       </c>
       <c r="H16" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3712013,2.1440509","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3812655,2.1526398","Open GSV")</f>
       </c>
       <c r="I16" t="s">
         <v>18</v>
@@ -2074,22 +2056,22 @@
         <v>62</v>
       </c>
       <c r="C17" t="s">
-        <v>37</v>
+        <v>49</v>
       </c>
       <c r="D17" t="s">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="E17" t="n">
-        <v>2.147403</v>
+        <v>2.1485936</v>
       </c>
       <c r="F17" t="n">
-        <v>41.3719318</v>
+        <v>41.3828476</v>
       </c>
       <c r="G17" t="s">
         <v>78</v>
       </c>
       <c r="H17" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3719318,2.147403","Open GSV")</f>
+        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936","Open GSV")</f>
       </c>
       <c r="I17" t="s">
         <v>18</v>
@@ -2099,210 +2081,6 @@
       <c r="L17"/>
       <c r="M17"/>
       <c r="N17"/>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>17</v>
-      </c>
-      <c r="B18" t="s">
-        <v>62</v>
-      </c>
-      <c r="C18" t="s">
-        <v>41</v>
-      </c>
-      <c r="D18" t="s">
-        <v>42</v>
-      </c>
-      <c r="E18" t="n">
-        <v>2.18071500409385</v>
-      </c>
-      <c r="F18" t="n">
-        <v>41.4059407666011</v>
-      </c>
-      <c r="G18" t="s">
-        <v>79</v>
-      </c>
-      <c r="H18" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.4059407666011,2.18071500409385","Open GSV")</f>
-      </c>
-      <c r="I18" t="s">
-        <v>18</v>
-      </c>
-      <c r="J18"/>
-      <c r="K18"/>
-      <c r="L18"/>
-      <c r="M18"/>
-      <c r="N18"/>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>18</v>
-      </c>
-      <c r="B19" t="s">
-        <v>62</v>
-      </c>
-      <c r="C19" t="s">
-        <v>45</v>
-      </c>
-      <c r="D19" t="s">
-        <v>42</v>
-      </c>
-      <c r="E19" t="n">
-        <v>2.1503529</v>
-      </c>
-      <c r="F19" t="n">
-        <v>41.3815253</v>
-      </c>
-      <c r="G19" t="s">
-        <v>80</v>
-      </c>
-      <c r="H19" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3815253,2.1503529","Open GSV")</f>
-      </c>
-      <c r="I19" t="s">
-        <v>18</v>
-      </c>
-      <c r="J19"/>
-      <c r="K19"/>
-      <c r="L19"/>
-      <c r="M19"/>
-      <c r="N19"/>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>19</v>
-      </c>
-      <c r="B20" t="s">
-        <v>62</v>
-      </c>
-      <c r="C20" t="s">
-        <v>45</v>
-      </c>
-      <c r="D20" t="s">
-        <v>42</v>
-      </c>
-      <c r="E20" t="n">
-        <v>2.1489247</v>
-      </c>
-      <c r="F20" t="n">
-        <v>41.3827831</v>
-      </c>
-      <c r="G20" t="s">
-        <v>81</v>
-      </c>
-      <c r="H20" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3827831,2.1489247","Open GSV")</f>
-      </c>
-      <c r="I20" t="s">
-        <v>18</v>
-      </c>
-      <c r="J20"/>
-      <c r="K20"/>
-      <c r="L20"/>
-      <c r="M20"/>
-      <c r="N20"/>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>20</v>
-      </c>
-      <c r="B21" t="s">
-        <v>62</v>
-      </c>
-      <c r="C21" t="s">
-        <v>47</v>
-      </c>
-      <c r="D21" t="s">
-        <v>42</v>
-      </c>
-      <c r="E21" t="n">
-        <v>2.1526398</v>
-      </c>
-      <c r="F21" t="n">
-        <v>41.3812655</v>
-      </c>
-      <c r="G21" t="s">
-        <v>82</v>
-      </c>
-      <c r="H21" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3812655,2.1526398","Open GSV")</f>
-      </c>
-      <c r="I21" t="s">
-        <v>18</v>
-      </c>
-      <c r="J21"/>
-      <c r="K21"/>
-      <c r="L21"/>
-      <c r="M21"/>
-      <c r="N21"/>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>21</v>
-      </c>
-      <c r="B22" t="s">
-        <v>62</v>
-      </c>
-      <c r="C22" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" t="s">
-        <v>42</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.1485936</v>
-      </c>
-      <c r="F22" t="n">
-        <v>41.3828476</v>
-      </c>
-      <c r="G22" t="s">
-        <v>83</v>
-      </c>
-      <c r="H22" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828476,2.1485936","Open GSV")</f>
-      </c>
-      <c r="I22" t="s">
-        <v>18</v>
-      </c>
-      <c r="J22"/>
-      <c r="K22"/>
-      <c r="L22"/>
-      <c r="M22"/>
-      <c r="N22"/>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>22</v>
-      </c>
-      <c r="B23" t="s">
-        <v>62</v>
-      </c>
-      <c r="C23" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.1481751</v>
-      </c>
-      <c r="F23" t="n">
-        <v>41.3828211</v>
-      </c>
-      <c r="G23" t="s">
-        <v>84</v>
-      </c>
-      <c r="H23" s="1" t="str">
-        <f>HYPERLINK("https://www.google.com/maps/@?api=1&amp;map_action=pano&amp;viewpoint=41.3828211,2.1481751","Open GSV")</f>
-      </c>
-      <c r="I23" t="s">
-        <v>18</v>
-      </c>
-      <c r="J23"/>
-      <c r="K23"/>
-      <c r="L23"/>
-      <c r="M23"/>
-      <c r="N23"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:N1"/>

--- a/outputs/barcelona_samples_2019_2023.xlsx
+++ b/outputs/barcelona_samples_2019_2023.xlsx
@@ -10,7 +10,7 @@
   <sheets>
     <sheet name="ADD" sheetId="1" state="visible" r:id="rId3"/>
     <sheet name="REMOVE" sheetId="2" state="visible" r:id="rId4"/>
-    <sheet name="GENERAL" sheetId="3" state="visible" r:id="rId5"/>
+    <sheet name="NONCI" sheetId="3" state="visible" r:id="rId5"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.001"/>
   <extLst>
